--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,2070 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129609708</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>668182</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6696450</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129609896</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>668165</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6696493</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129609237</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>668105</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6696462</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129609700</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>668182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6696446</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129609725</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>668191</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6696446</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129609244</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>668097</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6696476</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129609759</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>668197</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6696455</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129609164</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91098</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6039940</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mandarinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria tridentina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>668099</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6696458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129609702</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>668182</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6696446</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129609756</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6696457</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129609747</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129609743</v>
+      </c>
+      <c r="B14" t="n">
+        <v>105705</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129609112</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>668097</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6696453</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129609751</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129609663</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>668145</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6696429</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129609988</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>668154</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6696517</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129609745</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129609173</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>668102</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6696465</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129609100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>668105</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6696449</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609896</v>
+        <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>92508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,27 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668165</v>
+        <v>668105</v>
       </c>
       <c r="R4" t="n">
-        <v>6696493</v>
+        <v>6696462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609237</v>
+        <v>129609700</v>
       </c>
       <c r="B5" t="n">
         <v>92508</v>
@@ -1018,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1034,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668105</v>
+        <v>668182</v>
       </c>
       <c r="R5" t="n">
-        <v>6696462</v>
+        <v>6696446</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609700</v>
+        <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>92508</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668182</v>
+        <v>668165</v>
       </c>
       <c r="R6" t="n">
-        <v>6696446</v>
+        <v>6696493</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B9" t="n">
-        <v>92508</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,34 +1428,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R9" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1499,11 +1492,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>92508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,27 +1663,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R11" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609747</v>
+        <v>129609743</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>105705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,26 +1891,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1981,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609743</v>
+        <v>129609747</v>
       </c>
       <c r="B14" t="n">
-        <v>105705</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,27 +1993,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129609173</v>
       </c>
       <c r="B19" t="n">
-        <v>92508</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,34 +2535,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2570,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668102</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696465</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2633,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609173</v>
+        <v>129609745</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>92508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,31 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668102</v>
+        <v>668198</v>
       </c>
       <c r="R20" t="n">
-        <v>6696465</v>
+        <v>6696456</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>92536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,27 +1428,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R9" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1492,6 +1499,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,7 +1534,7 @@
         <v>129609164</v>
       </c>
       <c r="B10" t="n">
-        <v>91098</v>
+        <v>91126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B11" t="n">
-        <v>92508</v>
+        <v>98734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,34 +1675,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R11" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609743</v>
+        <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>105705</v>
+        <v>91354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,27 +1891,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1982,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609747</v>
+        <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>105734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,26 +1992,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609173</v>
+        <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>92536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,31 +2535,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2567,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668102</v>
+        <v>668198</v>
       </c>
       <c r="R19" t="n">
-        <v>6696465</v>
+        <v>6696456</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609745</v>
+        <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>92508</v>
+        <v>98734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2644,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668198</v>
+        <v>668102</v>
       </c>
       <c r="R20" t="n">
-        <v>6696456</v>
+        <v>6696465</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -2083,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609112</v>
+        <v>129609751</v>
       </c>
       <c r="B15" t="n">
-        <v>92536</v>
+        <v>100945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,34 +2094,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668097</v>
+        <v>668198</v>
       </c>
       <c r="R15" t="n">
-        <v>6696453</v>
+        <v>6696456</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609751</v>
+        <v>129609112</v>
       </c>
       <c r="B16" t="n">
-        <v>100945</v>
+        <v>92536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,27 +2196,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R16" t="n">
-        <v>6696456</v>
+        <v>6696453</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609988</v>
+        <v>129609173</v>
       </c>
       <c r="B18" t="n">
-        <v>92536</v>
+        <v>98734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,34 +2426,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,13 +2458,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668154</v>
+        <v>668102</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696465</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,7 +2521,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129609988</v>
       </c>
       <c r="B19" t="n">
         <v>92536</v>
@@ -2554,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,13 +2567,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668154</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696517</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609173</v>
+        <v>129609745</v>
       </c>
       <c r="B20" t="n">
-        <v>98734</v>
+        <v>92536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,31 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668102</v>
+        <v>668198</v>
       </c>
       <c r="R20" t="n">
-        <v>6696465</v>
+        <v>6696456</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,45 +1531,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609164</v>
+        <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>91126</v>
+        <v>98746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6039940</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668099</v>
+        <v>668182</v>
       </c>
       <c r="R10" t="n">
-        <v>6696458</v>
+        <v>6696446</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1610,44 +1603,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1664,38 +1633,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609702</v>
+        <v>129609164</v>
       </c>
       <c r="B11" t="n">
-        <v>98734</v>
+        <v>91132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>6039940</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668182</v>
+        <v>668099</v>
       </c>
       <c r="R11" t="n">
-        <v>6696446</v>
+        <v>6696458</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1736,20 +1712,44 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105734</v>
+        <v>105746</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609751</v>
       </c>
       <c r="B15" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>129609112</v>
       </c>
       <c r="B16" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609173</v>
+        <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>98734</v>
+        <v>92542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,31 +2426,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2458,13 +2461,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668102</v>
+        <v>668154</v>
       </c>
       <c r="R18" t="n">
-        <v>6696465</v>
+        <v>6696517</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609988</v>
+        <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2554,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2567,13 +2570,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668154</v>
+        <v>668198</v>
       </c>
       <c r="R19" t="n">
-        <v>6696517</v>
+        <v>6696456</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609745</v>
+        <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>92536</v>
+        <v>98746</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2644,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668198</v>
+        <v>668102</v>
       </c>
       <c r="R20" t="n">
-        <v>6696456</v>
+        <v>6696465</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,6 +2839,588 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129680871</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91360</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>668197</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6696458</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129680897</v>
+      </c>
+      <c r="B23" t="n">
+        <v>86840</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>668153</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6696478</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129680905</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87039</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>668149</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6696518</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129680875</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87002</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>668197</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6696458</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129680880</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87002</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>668200</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6696455</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609237</v>
+        <v>129609896</v>
       </c>
       <c r="B4" t="n">
-        <v>92542</v>
+        <v>98747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +897,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668105</v>
+        <v>668165</v>
       </c>
       <c r="R4" t="n">
-        <v>6696462</v>
+        <v>6696493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +991,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609896</v>
+        <v>129609237</v>
       </c>
       <c r="B6" t="n">
-        <v>98746</v>
+        <v>92543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,27 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668165</v>
+        <v>668105</v>
       </c>
       <c r="R6" t="n">
-        <v>6696493</v>
+        <v>6696462</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609759</v>
+        <v>129609164</v>
       </c>
       <c r="B9" t="n">
-        <v>92542</v>
+        <v>91133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6039940</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schild</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668197</v>
+        <v>668099</v>
       </c>
       <c r="R9" t="n">
-        <v>6696455</v>
+        <v>6696458</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,14 +1496,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,9 +1517,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1534,7 +1553,7 @@
         <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,37 +1652,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609164</v>
+        <v>129609759</v>
       </c>
       <c r="B11" t="n">
-        <v>91132</v>
+        <v>92543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6039940</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1679,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668099</v>
+        <v>668197</v>
       </c>
       <c r="R11" t="n">
-        <v>6696458</v>
+        <v>6696455</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1712,19 +1731,14 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:46</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,23 +1747,9 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105746</v>
+        <v>105747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609751</v>
+        <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>100957</v>
+        <v>92543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,27 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2122,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R15" t="n">
-        <v>6696456</v>
+        <v>6696453</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2185,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609112</v>
+        <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>92542</v>
+        <v>100958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,34 +2203,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668097</v>
+        <v>668198</v>
       </c>
       <c r="R16" t="n">
-        <v>6696453</v>
+        <v>6696456</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609988</v>
+        <v>129609745</v>
       </c>
       <c r="B18" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668154</v>
+        <v>668198</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696456</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129609988</v>
       </c>
       <c r="B19" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668154</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696517</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680897</v>
       </c>
       <c r="B23" t="n">
-        <v>86840</v>
+        <v>86841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680905</v>
       </c>
       <c r="B24" t="n">
-        <v>87039</v>
+        <v>87040</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>129680875</v>
       </c>
       <c r="B25" t="n">
-        <v>87002</v>
+        <v>87003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680880</v>
       </c>
       <c r="B26" t="n">
-        <v>87002</v>
+        <v>87003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609164</v>
+        <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>91133</v>
+        <v>92543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6039940</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668099</v>
+        <v>668197</v>
       </c>
       <c r="R9" t="n">
-        <v>6696458</v>
+        <v>6696455</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,19 +1496,14 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:46</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,23 +1512,9 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1550,38 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609702</v>
+        <v>129609164</v>
       </c>
       <c r="B10" t="n">
-        <v>98747</v>
+        <v>91133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>6039940</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668182</v>
+        <v>668099</v>
       </c>
       <c r="R10" t="n">
-        <v>6696446</v>
+        <v>6696458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,20 +1610,44 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1652,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B11" t="n">
-        <v>92543</v>
+        <v>98747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,34 +1675,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R11" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609896</v>
+        <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>98747</v>
+        <v>92548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,27 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668165</v>
+        <v>668105</v>
       </c>
       <c r="R4" t="n">
-        <v>6696493</v>
+        <v>6696462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,7 +998,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609237</v>
+        <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>92543</v>
+        <v>98752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668105</v>
+        <v>668165</v>
       </c>
       <c r="R6" t="n">
-        <v>6696462</v>
+        <v>6696493</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129609164</v>
       </c>
       <c r="B10" t="n">
-        <v>91133</v>
+        <v>91138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>129609702</v>
       </c>
       <c r="B11" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609747</v>
+        <v>129609743</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>105752</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,26 +1891,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1981,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609743</v>
+        <v>129609747</v>
       </c>
       <c r="B14" t="n">
-        <v>105747</v>
+        <v>91366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,27 +1993,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609112</v>
+        <v>129609751</v>
       </c>
       <c r="B15" t="n">
-        <v>92543</v>
+        <v>100963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,34 +2094,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668097</v>
+        <v>668198</v>
       </c>
       <c r="R15" t="n">
-        <v>6696453</v>
+        <v>6696456</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609751</v>
+        <v>129609112</v>
       </c>
       <c r="B16" t="n">
-        <v>100958</v>
+        <v>92548</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,27 +2196,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R16" t="n">
-        <v>6696456</v>
+        <v>6696453</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609745</v>
+        <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668198</v>
+        <v>668154</v>
       </c>
       <c r="R18" t="n">
-        <v>6696456</v>
+        <v>6696517</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609988</v>
+        <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668154</v>
+        <v>668198</v>
       </c>
       <c r="R19" t="n">
-        <v>6696517</v>
+        <v>6696456</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680897</v>
       </c>
       <c r="B23" t="n">
-        <v>86841</v>
+        <v>86846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680905</v>
       </c>
       <c r="B24" t="n">
-        <v>87040</v>
+        <v>87045</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>129680875</v>
       </c>
       <c r="B25" t="n">
-        <v>87003</v>
+        <v>87008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680880</v>
       </c>
       <c r="B26" t="n">
-        <v>87003</v>
+        <v>87008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609237</v>
+        <v>129609896</v>
       </c>
       <c r="B4" t="n">
-        <v>92548</v>
+        <v>98752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +897,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668105</v>
+        <v>668165</v>
       </c>
       <c r="R4" t="n">
-        <v>6696462</v>
+        <v>6696493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609700</v>
+        <v>129609237</v>
       </c>
       <c r="B5" t="n">
         <v>92548</v>
@@ -1025,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,13 +1034,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668182</v>
+        <v>668105</v>
       </c>
       <c r="R5" t="n">
-        <v>6696446</v>
+        <v>6696462</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609896</v>
+        <v>129609700</v>
       </c>
       <c r="B6" t="n">
-        <v>98752</v>
+        <v>92548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,27 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668165</v>
+        <v>668182</v>
       </c>
       <c r="R6" t="n">
-        <v>6696493</v>
+        <v>6696446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B9" t="n">
-        <v>92548</v>
+        <v>98752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,34 +1428,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R9" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1499,11 +1492,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B11" t="n">
-        <v>98752</v>
+        <v>92548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,27 +1663,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R11" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609743</v>
+        <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>105752</v>
+        <v>91366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,27 +1891,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1982,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609747</v>
+        <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>91366</v>
+        <v>105752</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,26 +1992,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609751</v>
+        <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>100963</v>
+        <v>92548</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,27 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2122,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R15" t="n">
-        <v>6696456</v>
+        <v>6696453</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2185,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609112</v>
+        <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>92548</v>
+        <v>100963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,34 +2203,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668097</v>
+        <v>668198</v>
       </c>
       <c r="R16" t="n">
-        <v>6696453</v>
+        <v>6696456</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609988</v>
+        <v>129609173</v>
       </c>
       <c r="B18" t="n">
-        <v>92548</v>
+        <v>98752</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,34 +2426,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,13 +2458,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668154</v>
+        <v>668102</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696465</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,7 +2521,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129609988</v>
       </c>
       <c r="B19" t="n">
         <v>92548</v>
@@ -2554,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,13 +2567,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668154</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696517</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609173</v>
+        <v>129609745</v>
       </c>
       <c r="B20" t="n">
-        <v>98752</v>
+        <v>92548</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,31 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668102</v>
+        <v>668198</v>
       </c>
       <c r="R20" t="n">
-        <v>6696465</v>
+        <v>6696456</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609896</v>
+        <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>98752</v>
+        <v>92548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,27 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668165</v>
+        <v>668105</v>
       </c>
       <c r="R4" t="n">
-        <v>6696493</v>
+        <v>6696462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609237</v>
+        <v>129609700</v>
       </c>
       <c r="B5" t="n">
         <v>92548</v>
@@ -1018,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1034,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668105</v>
+        <v>668182</v>
       </c>
       <c r="R5" t="n">
-        <v>6696462</v>
+        <v>6696446</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609700</v>
+        <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>92548</v>
+        <v>98752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668182</v>
+        <v>668165</v>
       </c>
       <c r="R6" t="n">
-        <v>6696446</v>
+        <v>6696493</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>98752</v>
+        <v>92548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,27 +1428,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R9" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1492,6 +1499,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B11" t="n">
-        <v>92548</v>
+        <v>98752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,34 +1675,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R11" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609173</v>
+        <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>98752</v>
+        <v>92548</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,31 +2426,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2458,13 +2461,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668102</v>
+        <v>668154</v>
       </c>
       <c r="R18" t="n">
-        <v>6696465</v>
+        <v>6696517</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,7 +2524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609988</v>
+        <v>129609745</v>
       </c>
       <c r="B19" t="n">
         <v>92548</v>
@@ -2551,7 +2554,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2567,13 +2570,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668154</v>
+        <v>668198</v>
       </c>
       <c r="R19" t="n">
-        <v>6696517</v>
+        <v>6696456</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609745</v>
+        <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>92548</v>
+        <v>98752</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2644,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668198</v>
+        <v>668102</v>
       </c>
       <c r="R20" t="n">
-        <v>6696456</v>
+        <v>6696465</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609759</v>
+        <v>129609164</v>
       </c>
       <c r="B9" t="n">
-        <v>92548</v>
+        <v>91138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6039940</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schild</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668197</v>
+        <v>668099</v>
       </c>
       <c r="R9" t="n">
-        <v>6696455</v>
+        <v>6696458</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,14 +1496,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,9 +1517,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1531,37 +1550,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609164</v>
+        <v>129609759</v>
       </c>
       <c r="B10" t="n">
-        <v>91138</v>
+        <v>92548</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6039940</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1577,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668099</v>
+        <v>668197</v>
       </c>
       <c r="R10" t="n">
-        <v>6696458</v>
+        <v>6696455</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1610,19 +1629,14 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:46</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,23 +1645,9 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609164</v>
+        <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>91138</v>
+        <v>92552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6039940</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668099</v>
+        <v>668197</v>
       </c>
       <c r="R9" t="n">
-        <v>6696458</v>
+        <v>6696455</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,19 +1496,14 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:46</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,23 +1512,9 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1550,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>92548</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,34 +1542,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1596,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R10" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,11 +1606,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,38 +1633,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609702</v>
+        <v>129609164</v>
       </c>
       <c r="B11" t="n">
-        <v>98752</v>
+        <v>91142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>6039940</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668182</v>
+        <v>668099</v>
       </c>
       <c r="R11" t="n">
-        <v>6696446</v>
+        <v>6696458</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1736,20 +1712,44 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105752</v>
+        <v>105756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609988</v>
+        <v>129609173</v>
       </c>
       <c r="B18" t="n">
-        <v>92548</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,34 +2426,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,13 +2458,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668154</v>
+        <v>668102</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696465</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129609988</v>
       </c>
       <c r="B19" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,13 +2567,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668154</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696517</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609173</v>
+        <v>129609745</v>
       </c>
       <c r="B20" t="n">
-        <v>98752</v>
+        <v>92552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,31 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668102</v>
+        <v>668198</v>
       </c>
       <c r="R20" t="n">
-        <v>6696465</v>
+        <v>6696456</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680897</v>
       </c>
       <c r="B23" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680905</v>
       </c>
       <c r="B24" t="n">
-        <v>87045</v>
+        <v>87049</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>129680875</v>
       </c>
       <c r="B25" t="n">
-        <v>87008</v>
+        <v>87012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680880</v>
       </c>
       <c r="B26" t="n">
-        <v>87008</v>
+        <v>87012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>129609164</v>
       </c>
       <c r="B11" t="n">
-        <v>91142</v>
+        <v>91144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105756</v>
+        <v>105758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609173</v>
+        <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>92554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,31 +2426,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2458,13 +2461,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668102</v>
+        <v>668154</v>
       </c>
       <c r="R18" t="n">
-        <v>6696465</v>
+        <v>6696517</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609988</v>
+        <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2554,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2567,13 +2570,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668154</v>
+        <v>668198</v>
       </c>
       <c r="R19" t="n">
-        <v>6696517</v>
+        <v>6696456</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609745</v>
+        <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>92552</v>
+        <v>98758</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2644,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668198</v>
+        <v>668102</v>
       </c>
       <c r="R20" t="n">
-        <v>6696456</v>
+        <v>6696465</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680897</v>
       </c>
       <c r="B23" t="n">
-        <v>86850</v>
+        <v>86852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680905</v>
       </c>
       <c r="B24" t="n">
-        <v>87049</v>
+        <v>87051</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>129680875</v>
       </c>
       <c r="B25" t="n">
-        <v>87012</v>
+        <v>87014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680880</v>
       </c>
       <c r="B26" t="n">
-        <v>87012</v>
+        <v>87014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609237</v>
+        <v>129609896</v>
       </c>
       <c r="B4" t="n">
-        <v>92554</v>
+        <v>98758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +897,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668105</v>
+        <v>668165</v>
       </c>
       <c r="R4" t="n">
-        <v>6696462</v>
+        <v>6696493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609700</v>
+        <v>129609237</v>
       </c>
       <c r="B5" t="n">
         <v>92554</v>
@@ -1025,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,13 +1034,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668182</v>
+        <v>668105</v>
       </c>
       <c r="R5" t="n">
-        <v>6696446</v>
+        <v>6696462</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609896</v>
+        <v>129609700</v>
       </c>
       <c r="B6" t="n">
-        <v>98758</v>
+        <v>92554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,27 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668165</v>
+        <v>668182</v>
       </c>
       <c r="R6" t="n">
-        <v>6696493</v>
+        <v>6696446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609112</v>
+        <v>129609751</v>
       </c>
       <c r="B15" t="n">
-        <v>92554</v>
+        <v>100969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,34 +2094,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668097</v>
+        <v>668198</v>
       </c>
       <c r="R15" t="n">
-        <v>6696453</v>
+        <v>6696456</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609751</v>
+        <v>129609112</v>
       </c>
       <c r="B16" t="n">
-        <v>100969</v>
+        <v>92554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,27 +2196,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R16" t="n">
-        <v>6696456</v>
+        <v>6696453</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609988</v>
+        <v>129609173</v>
       </c>
       <c r="B18" t="n">
-        <v>92554</v>
+        <v>98758</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,34 +2426,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,13 +2458,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668154</v>
+        <v>668102</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696465</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,7 +2521,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129609988</v>
       </c>
       <c r="B19" t="n">
         <v>92554</v>
@@ -2554,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,13 +2567,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668154</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696517</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609173</v>
+        <v>129609745</v>
       </c>
       <c r="B20" t="n">
-        <v>98758</v>
+        <v>92554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,31 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668102</v>
+        <v>668198</v>
       </c>
       <c r="R20" t="n">
-        <v>6696465</v>
+        <v>6696456</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609896</v>
+        <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>98758</v>
+        <v>92554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,27 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668165</v>
+        <v>668105</v>
       </c>
       <c r="R4" t="n">
-        <v>6696493</v>
+        <v>6696462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609237</v>
+        <v>129609700</v>
       </c>
       <c r="B5" t="n">
         <v>92554</v>
@@ -1018,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1034,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668105</v>
+        <v>668182</v>
       </c>
       <c r="R5" t="n">
-        <v>6696462</v>
+        <v>6696446</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609700</v>
+        <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>92554</v>
+        <v>98758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668182</v>
+        <v>668165</v>
       </c>
       <c r="R6" t="n">
-        <v>6696446</v>
+        <v>6696493</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609751</v>
+        <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>100969</v>
+        <v>92554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,27 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2122,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R15" t="n">
-        <v>6696456</v>
+        <v>6696453</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2185,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609112</v>
+        <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>92554</v>
+        <v>100969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,34 +2203,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668097</v>
+        <v>668198</v>
       </c>
       <c r="R16" t="n">
-        <v>6696453</v>
+        <v>6696456</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609237</v>
+        <v>129609896</v>
       </c>
       <c r="B4" t="n">
-        <v>92554</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +897,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668105</v>
+        <v>668165</v>
       </c>
       <c r="R4" t="n">
-        <v>6696462</v>
+        <v>6696493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609700</v>
+        <v>129609237</v>
       </c>
       <c r="B5" t="n">
         <v>92554</v>
@@ -1025,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,13 +1034,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668182</v>
+        <v>668105</v>
       </c>
       <c r="R5" t="n">
-        <v>6696446</v>
+        <v>6696462</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609896</v>
+        <v>129609700</v>
       </c>
       <c r="B6" t="n">
-        <v>98758</v>
+        <v>92554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,27 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668165</v>
+        <v>668182</v>
       </c>
       <c r="R6" t="n">
-        <v>6696493</v>
+        <v>6696446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105758</v>
+        <v>105768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609173</v>
+        <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>98758</v>
+        <v>92554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,31 +2426,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2458,13 +2461,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668102</v>
+        <v>668154</v>
       </c>
       <c r="R18" t="n">
-        <v>6696465</v>
+        <v>6696517</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,7 +2524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609988</v>
+        <v>129609745</v>
       </c>
       <c r="B19" t="n">
         <v>92554</v>
@@ -2551,7 +2554,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2567,13 +2570,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668154</v>
+        <v>668198</v>
       </c>
       <c r="R19" t="n">
-        <v>6696517</v>
+        <v>6696456</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609745</v>
+        <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>92554</v>
+        <v>98768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2644,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668198</v>
+        <v>668102</v>
       </c>
       <c r="R20" t="n">
-        <v>6696456</v>
+        <v>6696465</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609759</v>
+        <v>129609164</v>
       </c>
       <c r="B9" t="n">
-        <v>92554</v>
+        <v>91144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6039940</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schild</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668197</v>
+        <v>668099</v>
       </c>
       <c r="R9" t="n">
-        <v>6696455</v>
+        <v>6696458</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,14 +1496,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,9 +1517,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1531,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>92554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,27 +1561,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R10" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1606,6 +1632,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,45 +1664,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609164</v>
+        <v>129609702</v>
       </c>
       <c r="B11" t="n">
-        <v>91144</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6039940</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1679,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668099</v>
+        <v>668182</v>
       </c>
       <c r="R11" t="n">
-        <v>6696458</v>
+        <v>6696446</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1712,44 +1736,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>92554</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,34 +1561,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1596,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R10" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,11 +1625,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>92554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,27 +1663,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R11" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92917</v>
+        <v>92920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609896</v>
+        <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>92557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,27 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668165</v>
+        <v>668105</v>
       </c>
       <c r="R4" t="n">
-        <v>6696493</v>
+        <v>6696462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609237</v>
+        <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1034,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668105</v>
+        <v>668182</v>
       </c>
       <c r="R5" t="n">
-        <v>6696462</v>
+        <v>6696446</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609700</v>
+        <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>92554</v>
+        <v>98772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668182</v>
+        <v>668165</v>
       </c>
       <c r="R6" t="n">
-        <v>6696446</v>
+        <v>6696493</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129609164</v>
       </c>
       <c r="B9" t="n">
-        <v>91144</v>
+        <v>91147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>129609759</v>
       </c>
       <c r="B11" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105768</v>
+        <v>105772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680897</v>
       </c>
       <c r="B23" t="n">
-        <v>86852</v>
+        <v>86855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680905</v>
       </c>
       <c r="B24" t="n">
-        <v>87051</v>
+        <v>87054</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>129680875</v>
       </c>
       <c r="B25" t="n">
-        <v>87014</v>
+        <v>87017</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680880</v>
       </c>
       <c r="B26" t="n">
-        <v>87014</v>
+        <v>87017</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B10" t="n">
-        <v>98772</v>
+        <v>92557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,27 +1561,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R10" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1625,6 +1632,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609759</v>
+        <v>129609702</v>
       </c>
       <c r="B11" t="n">
-        <v>92557</v>
+        <v>98772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,34 +1675,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668197</v>
+        <v>668182</v>
       </c>
       <c r="R11" t="n">
-        <v>6696455</v>
+        <v>6696446</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>129609237</v>
       </c>
       <c r="B4" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129609700</v>
       </c>
       <c r="B5" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129609896</v>
       </c>
       <c r="B6" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,45 +1417,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609164</v>
+        <v>129609702</v>
       </c>
       <c r="B9" t="n">
-        <v>91147</v>
+        <v>98775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6039940</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668099</v>
+        <v>668182</v>
       </c>
       <c r="R9" t="n">
-        <v>6696458</v>
+        <v>6696446</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,44 +1489,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1550,37 +1519,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609759</v>
+        <v>129609164</v>
       </c>
       <c r="B10" t="n">
-        <v>92557</v>
+        <v>91150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>6039940</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schild</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1596,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668197</v>
+        <v>668099</v>
       </c>
       <c r="R10" t="n">
-        <v>6696455</v>
+        <v>6696458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,14 +1598,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,9 +1619,23 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1664,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B11" t="n">
-        <v>98772</v>
+        <v>92560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,27 +1663,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R11" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609747</v>
+        <v>129609743</v>
       </c>
       <c r="B13" t="n">
-        <v>91375</v>
+        <v>105775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,26 +1891,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1981,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609743</v>
+        <v>129609747</v>
       </c>
       <c r="B14" t="n">
-        <v>105772</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,27 +1993,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680897</v>
       </c>
       <c r="B23" t="n">
-        <v>86855</v>
+        <v>86858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680905</v>
       </c>
       <c r="B24" t="n">
-        <v>87054</v>
+        <v>87057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>129680875</v>
       </c>
       <c r="B25" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680880</v>
       </c>
       <c r="B26" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1417,38 +1417,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609702</v>
+        <v>129609164</v>
       </c>
       <c r="B9" t="n">
-        <v>98775</v>
+        <v>91150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>6039940</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668182</v>
+        <v>668099</v>
       </c>
       <c r="R9" t="n">
-        <v>6696446</v>
+        <v>6696458</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1489,20 +1496,44 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1519,45 +1550,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609164</v>
+        <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>91150</v>
+        <v>98775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6039940</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1565,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668099</v>
+        <v>668182</v>
       </c>
       <c r="R10" t="n">
-        <v>6696458</v>
+        <v>6696446</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1598,44 +1622,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -1417,45 +1417,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609164</v>
+        <v>129609702</v>
       </c>
       <c r="B9" t="n">
-        <v>91150</v>
+        <v>98775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6039940</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668099</v>
+        <v>668182</v>
       </c>
       <c r="R9" t="n">
-        <v>6696458</v>
+        <v>6696446</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,44 +1489,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1550,38 +1519,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609702</v>
+        <v>129609164</v>
       </c>
       <c r="B10" t="n">
-        <v>98775</v>
+        <v>91150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>6039940</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668182</v>
+        <v>668099</v>
       </c>
       <c r="R10" t="n">
-        <v>6696446</v>
+        <v>6696458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,20 +1598,44 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609743</v>
+        <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>105775</v>
+        <v>91378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,27 +1891,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1982,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609747</v>
+        <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>105775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,26 +1992,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129609708</v>
       </c>
       <c r="B3" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609237</v>
+        <v>129609896</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>98776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +897,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668105</v>
+        <v>668165</v>
       </c>
       <c r="R4" t="n">
-        <v>6696462</v>
+        <v>6696493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609700</v>
+        <v>129609237</v>
       </c>
       <c r="B5" t="n">
-        <v>92560</v>
+        <v>92561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,13 +1034,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668182</v>
+        <v>668105</v>
       </c>
       <c r="R5" t="n">
-        <v>6696446</v>
+        <v>6696462</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609896</v>
+        <v>129609700</v>
       </c>
       <c r="B6" t="n">
-        <v>98775</v>
+        <v>92561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,27 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668165</v>
+        <v>668182</v>
       </c>
       <c r="R6" t="n">
-        <v>6696493</v>
+        <v>6696446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129609725</v>
       </c>
       <c r="B7" t="n">
-        <v>92560</v>
+        <v>92561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129609244</v>
       </c>
       <c r="B8" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609702</v>
+        <v>129609759</v>
       </c>
       <c r="B9" t="n">
-        <v>98775</v>
+        <v>92561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,27 +1428,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668182</v>
+        <v>668197</v>
       </c>
       <c r="R9" t="n">
-        <v>6696446</v>
+        <v>6696455</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1492,6 +1499,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,45 +1531,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609164</v>
+        <v>129609702</v>
       </c>
       <c r="B10" t="n">
-        <v>91150</v>
+        <v>98776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6039940</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1565,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668099</v>
+        <v>668182</v>
       </c>
       <c r="R10" t="n">
-        <v>6696458</v>
+        <v>6696446</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1598,44 +1603,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1652,37 +1633,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609759</v>
+        <v>129609164</v>
       </c>
       <c r="B11" t="n">
-        <v>92560</v>
+        <v>91151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>6039940</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schild</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1698,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668197</v>
+        <v>668099</v>
       </c>
       <c r="R11" t="n">
-        <v>6696455</v>
+        <v>6696458</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1731,14 +1712,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,9 +1733,23 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>129609756</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129609747</v>
       </c>
       <c r="B13" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129609743</v>
       </c>
       <c r="B14" t="n">
-        <v>105775</v>
+        <v>105776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129609112</v>
       </c>
       <c r="B15" t="n">
-        <v>92560</v>
+        <v>92561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129609751</v>
       </c>
       <c r="B16" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129609663</v>
       </c>
       <c r="B17" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>129609988</v>
       </c>
       <c r="B18" t="n">
-        <v>92560</v>
+        <v>92561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129609745</v>
       </c>
       <c r="B19" t="n">
-        <v>92560</v>
+        <v>92561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>129609173</v>
       </c>
       <c r="B20" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129609100</v>
       </c>
       <c r="B21" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,37 +2942,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129680897</v>
+        <v>129680905</v>
       </c>
       <c r="B23" t="n">
-        <v>86858</v>
+        <v>87058</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668153</v>
+        <v>668149</v>
       </c>
       <c r="R23" t="n">
-        <v>6696478</v>
+        <v>6696518</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3066,37 +3066,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129680905</v>
+        <v>129680875</v>
       </c>
       <c r="B24" t="n">
-        <v>87057</v>
+        <v>87021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668149</v>
+        <v>668197</v>
       </c>
       <c r="R24" t="n">
-        <v>6696518</v>
+        <v>6696458</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3145,19 +3145,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,11 +3159,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3190,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129680875</v>
+        <v>129680880</v>
       </c>
       <c r="B25" t="n">
-        <v>87020</v>
+        <v>87021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3205,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3236,10 +3221,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668197</v>
+        <v>668200</v>
       </c>
       <c r="R25" t="n">
-        <v>6696458</v>
+        <v>6696455</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3269,9 +3254,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3283,6 +3278,11 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3299,10 +3299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129680880</v>
+        <v>129680897</v>
       </c>
       <c r="B26" t="n">
-        <v>87020</v>
+        <v>86859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,26 +3310,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668200</v>
+        <v>668153</v>
       </c>
       <c r="R26" t="n">
-        <v>6696455</v>
+        <v>6696478</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,13 +3399,22 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>Kollekt sparat</t>
+          <t>BB-1082</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3419,7 +3428,11 @@
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -2844,7 +2844,7 @@
         <v>129680871</v>
       </c>
       <c r="B22" t="n">
-        <v>91379</v>
+        <v>91396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129680905</v>
       </c>
       <c r="B23" t="n">
-        <v>87058</v>
+        <v>87075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129680875</v>
       </c>
       <c r="B24" t="n">
-        <v>87021</v>
+        <v>87038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>129680880</v>
       </c>
       <c r="B25" t="n">
-        <v>87021</v>
+        <v>87038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129680897</v>
       </c>
       <c r="B26" t="n">
-        <v>86859</v>
+        <v>86876</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3302,7 +3302,7 @@
         <v>129680897</v>
       </c>
       <c r="B26" t="n">
-        <v>86892</v>
+        <v>86979</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3434,6 +3434,409 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132466279</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96534</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>210</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>668170</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6696466</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132466278</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106134</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>668161</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6696451</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132466301</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>668162</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6696453</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132466303</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>668165</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6696429</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106134</v>
+        <v>106142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106142</v>
+        <v>106153</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106153</v>
+        <v>106154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106154</v>
+        <v>106155</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106155</v>
+        <v>106156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96554</v>
+        <v>96555</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106156</v>
+        <v>106157</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96555</v>
+        <v>96557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106157</v>
+        <v>106159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>132466279</v>
       </c>
       <c r="B27" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>132466278</v>
       </c>
       <c r="B28" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>132466301</v>
       </c>
       <c r="B29" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>132466303</v>
       </c>
       <c r="B30" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124393208</v>
+        <v>124393187</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668133</v>
+        <v>668151</v>
       </c>
       <c r="R2" t="n">
-        <v>6696416</v>
+        <v>6696537</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129609708</v>
+        <v>132466279</v>
       </c>
       <c r="B3" t="n">
-        <v>92924</v>
+        <v>96629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,48 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668182</v>
+        <v>668170</v>
       </c>
       <c r="R3" t="n">
-        <v>6696450</v>
+        <v>6696466</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,29 +866,43 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129609896</v>
+        <v>129609663</v>
       </c>
       <c r="B4" t="n">
-        <v>98776</v>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,27 +910,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668165</v>
+        <v>668145</v>
       </c>
       <c r="R4" t="n">
-        <v>6696493</v>
+        <v>6696429</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,6 +984,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -988,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129609237</v>
+        <v>132466255</v>
       </c>
       <c r="B5" t="n">
-        <v>92561</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,48 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668105</v>
+        <v>668161</v>
       </c>
       <c r="R5" t="n">
-        <v>6696462</v>
+        <v>6696451</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,29 +1099,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129609700</v>
+        <v>132466256</v>
       </c>
       <c r="B6" t="n">
-        <v>92561</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,48 +1128,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668182</v>
+        <v>668165</v>
       </c>
       <c r="R6" t="n">
-        <v>6696446</v>
+        <v>6696432</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,29 +1196,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129609725</v>
+        <v>124393169</v>
       </c>
       <c r="B7" t="n">
-        <v>92561</v>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,48 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668191</v>
+        <v>668156</v>
       </c>
       <c r="R7" t="n">
-        <v>6696446</v>
+        <v>6696531</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,29 +1293,43 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129609244</v>
+        <v>124393171</v>
       </c>
       <c r="B8" t="n">
-        <v>100987</v>
+        <v>96458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,41 +1337,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668097</v>
+        <v>668156</v>
       </c>
       <c r="R8" t="n">
-        <v>6696476</v>
+        <v>6696405</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,29 +1405,43 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129609759</v>
+        <v>129609747</v>
       </c>
       <c r="B9" t="n">
-        <v>92561</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,33 +1449,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668197</v>
+        <v>668198</v>
       </c>
       <c r="R9" t="n">
-        <v>6696455</v>
+        <v>6696456</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1499,11 +1512,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis 40 frk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129609702</v>
+        <v>129609769</v>
       </c>
       <c r="B10" t="n">
-        <v>98776</v>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,27 +1550,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668182</v>
+        <v>668210</v>
       </c>
       <c r="R10" t="n">
-        <v>6696446</v>
+        <v>6696444</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,44 +1640,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129609164</v>
+        <v>129609795</v>
       </c>
       <c r="B11" t="n">
-        <v>91151</v>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6039940</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1679,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668099</v>
+        <v>668206</v>
       </c>
       <c r="R11" t="n">
-        <v>6696458</v>
+        <v>6696477</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1712,44 +1711,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1766,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129609756</v>
+        <v>129609938</v>
       </c>
       <c r="B12" t="n">
-        <v>98832</v>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,39 +1752,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1817,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668198</v>
+        <v>668185</v>
       </c>
       <c r="R12" t="n">
-        <v>6696457</v>
+        <v>6696506</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1880,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129609747</v>
+        <v>129609969</v>
       </c>
       <c r="B13" t="n">
-        <v>91379</v>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668198</v>
+        <v>668169</v>
       </c>
       <c r="R13" t="n">
-        <v>6696456</v>
+        <v>6696511</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129609743</v>
+        <v>129680871</v>
       </c>
       <c r="B14" t="n">
-        <v>105776</v>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,27 +1954,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668198</v>
+        <v>668197</v>
       </c>
       <c r="R14" t="n">
-        <v>6696456</v>
+        <v>6696458</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2050,12 +2011,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2083,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129609112</v>
+        <v>129680862</v>
       </c>
       <c r="B15" t="n">
-        <v>92561</v>
+        <v>87309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,21 +2055,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2129,10 +2090,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668097</v>
+        <v>668181</v>
       </c>
       <c r="R15" t="n">
-        <v>6696453</v>
+        <v>6696507</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,12 +2120,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129609751</v>
+        <v>129680875</v>
       </c>
       <c r="B16" t="n">
-        <v>100987</v>
+        <v>87309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,27 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668198</v>
+        <v>668197</v>
       </c>
       <c r="R16" t="n">
-        <v>6696456</v>
+        <v>6696458</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2261,12 +2229,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129609663</v>
+        <v>129680880</v>
       </c>
       <c r="B17" t="n">
-        <v>92256</v>
+        <v>87309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,25 +2273,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2332,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668145</v>
+        <v>668200</v>
       </c>
       <c r="R17" t="n">
-        <v>6696429</v>
+        <v>6696455</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2362,12 +2338,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,24 +2366,9 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2415,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129609988</v>
+        <v>129680915</v>
       </c>
       <c r="B18" t="n">
-        <v>92561</v>
+        <v>87309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,26 +2397,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2461,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668154</v>
+        <v>668167</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696523</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,12 +2462,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129609745</v>
+        <v>129680931</v>
       </c>
       <c r="B19" t="n">
-        <v>92561</v>
+        <v>87309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2516,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2570,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668198</v>
+        <v>668184</v>
       </c>
       <c r="R19" t="n">
-        <v>6696456</v>
+        <v>6696513</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2600,12 +2581,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129609173</v>
+        <v>129680897</v>
       </c>
       <c r="B20" t="n">
-        <v>98776</v>
+        <v>87146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,31 +2635,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668102</v>
+        <v>668153</v>
       </c>
       <c r="R20" t="n">
-        <v>6696465</v>
+        <v>6696478</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2706,12 +2700,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,9 +2724,23 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>BB-1082</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2735,14 +2753,18 @@
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - 1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129609100</v>
+        <v>129680918</v>
       </c>
       <c r="B21" t="n">
-        <v>100987</v>
+        <v>87146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,27 +2772,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2778,13 +2807,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668105</v>
+        <v>668162</v>
       </c>
       <c r="R21" t="n">
-        <v>6696449</v>
+        <v>6696519</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2808,12 +2837,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,6 +2864,11 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2841,36 +2885,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129680871</v>
+        <v>129610394</v>
       </c>
       <c r="B22" t="n">
-        <v>91401</v>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2879,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668197</v>
+        <v>668132</v>
       </c>
       <c r="R22" t="n">
-        <v>6696458</v>
+        <v>6696568</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2909,12 +2961,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,37 +2994,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129680905</v>
+        <v>129608985</v>
       </c>
       <c r="B23" t="n">
-        <v>87080</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2988,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668149</v>
+        <v>668110</v>
       </c>
       <c r="R23" t="n">
-        <v>6696518</v>
+        <v>6696418</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,22 +3070,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,11 +3087,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3066,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129680875</v>
+        <v>129609069</v>
       </c>
       <c r="B24" t="n">
-        <v>87043</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3077,26 +3114,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3112,10 +3149,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668197</v>
+        <v>668078</v>
       </c>
       <c r="R24" t="n">
-        <v>6696458</v>
+        <v>6696419</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3142,12 +3179,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129680880</v>
+        <v>129609112</v>
       </c>
       <c r="B25" t="n">
-        <v>87043</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,26 +3223,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3221,10 +3258,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668200</v>
+        <v>668097</v>
       </c>
       <c r="R25" t="n">
-        <v>6696455</v>
+        <v>6696453</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3251,22 +3288,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,11 +3305,6 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3299,10 +3321,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129680897</v>
+        <v>129609237</v>
       </c>
       <c r="B26" t="n">
-        <v>86979</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,26 +3332,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3345,13 +3367,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668153</v>
+        <v>668105</v>
       </c>
       <c r="R26" t="n">
-        <v>6696478</v>
+        <v>6696462</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3375,22 +3397,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,23 +3411,9 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>barcode</t>
-        </is>
-      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>Björn Bråvander</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>BB-1082</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3428,18 +3426,14 @@
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - 1</t>
-        </is>
-      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132466279</v>
+        <v>129609302</v>
       </c>
       <c r="B27" t="n">
-        <v>96564</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,37 +3441,48 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668170</v>
+        <v>668137</v>
       </c>
       <c r="R27" t="n">
-        <v>6696466</v>
+        <v>6696419</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,12 +3506,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3515,43 +3520,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132466278</v>
+        <v>129609692</v>
       </c>
       <c r="B28" t="n">
-        <v>106170</v>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,37 +3550,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221141</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668161</v>
+        <v>668168</v>
       </c>
       <c r="R28" t="n">
-        <v>6696451</v>
+        <v>6696425</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3613,12 +3615,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,28 +3629,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132466301</v>
+        <v>129609700</v>
       </c>
       <c r="B29" t="n">
-        <v>101338</v>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,37 +3659,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668162</v>
+        <v>668182</v>
       </c>
       <c r="R29" t="n">
-        <v>6696453</v>
+        <v>6696446</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3710,12 +3724,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,28 +3738,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132466303</v>
+        <v>129609715</v>
       </c>
       <c r="B30" t="n">
-        <v>101338</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,37 +3768,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668165</v>
+        <v>668191</v>
       </c>
       <c r="R30" t="n">
-        <v>6696429</v>
+        <v>6696437</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3807,12 +3833,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,21 +3847,5463 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129609725</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>668191</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6696446</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129609745</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129609759</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>668197</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6696455</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 40 frk</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129609771</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>668210</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6696444</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129609794</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>668206</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6696477</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129609831</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>668186</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6696475</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129609920</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>668179</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6696523</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129609986</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>668169</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6696511</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129609988</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>668154</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6696517</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129609351</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>668141</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6696401</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129609027</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>668087</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6696419</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129609091</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>668081</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6696434</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129609296</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>668139</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6696414</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129609299</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>668139</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6696407</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129609313</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>668144</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6696410</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129609318</v>
+      </c>
+      <c r="B46" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>668134</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6696397</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129609708</v>
+      </c>
+      <c r="B47" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>668182</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6696450</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129610357</v>
+      </c>
+      <c r="B48" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>668132</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6696568</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129680912</v>
+      </c>
+      <c r="B49" t="n">
+        <v>93307</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>668159</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6696523</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129680938</v>
+      </c>
+      <c r="B50" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>668148</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6696556</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132466244</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>668150</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6696399</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>Ingemar Södergren</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>Ingemar Södergren</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129609007</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>668099</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6696406</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120208775</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>668180</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6696501</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120208776</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>668186</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6696508</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129609173</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>668102</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6696465</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129609694</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>668168</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6696425</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129609702</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>668182</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6696446</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129609896</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>668165</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6696493</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129609756</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6696457</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129609743</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132466278</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>668161</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6696451</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120208682</v>
+      </c>
+      <c r="B62" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>668186</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6696508</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129608936</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>668116</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6696401</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120208739</v>
+      </c>
+      <c r="B64" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>668166</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6696498</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129609325</v>
+      </c>
+      <c r="B65" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>668136</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6696404</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124393207</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>668159</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6696419</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124393208</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>668133</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6696416</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129608923</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>668123</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6696411</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129609001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>668099</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6696406</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129609073</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>668078</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6696419</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129609100</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>668105</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6696449</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129609244</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>668097</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6696476</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129609548</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>668152</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6696412</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129609695</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>668168</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6696425</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129609751</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132466301</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>668162</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6696453</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132466303</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>668165</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6696429</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129609783</v>
+      </c>
+      <c r="B78" t="n">
+        <v>89141</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>668212</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6696450</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129680905</v>
+      </c>
+      <c r="B79" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>668149</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6696518</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129707800</v>
+      </c>
+      <c r="B80" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>668173</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6696522</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Hotspot; kalkbarrskog; Under gran</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129609164</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91445</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6039940</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mandarinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ramaria tridentina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>668099</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6696458</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124393187</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609663</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466255</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466256</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124393169</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124393171</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609747</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609769</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,6 +1788,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609795</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609938</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609969</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680871</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680862</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,6 +2334,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680875</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2383,6 +2463,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680880</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2502,6 +2587,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680915</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2621,6 +2711,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680931</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2758,6 +2853,11 @@
           <t>Fynd med DNA-sekvens - 1</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680897</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2882,6 +2982,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680918</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2991,6 +3096,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129610394</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3100,6 +3210,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129608985</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3209,6 +3324,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3318,6 +3438,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609112</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,6 +3552,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609237</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3536,6 +3666,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609302</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3645,6 +3780,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609692</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3754,6 +3894,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609700</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3863,6 +4008,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609715</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3972,6 +4122,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609725</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4081,6 +4236,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609745</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4195,6 +4355,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609759</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4304,6 +4469,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609771</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4413,6 +4583,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609794</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4522,6 +4697,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609831</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4631,6 +4811,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609920</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4740,6 +4925,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609986</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4849,6 +5039,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609988</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4958,6 +5153,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609351</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5067,6 +5267,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609027</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5176,6 +5381,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609091</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5285,6 +5495,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609296</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5394,6 +5609,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609299</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5503,6 +5723,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609313</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5612,6 +5837,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609318</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5721,6 +5951,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609708</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5830,6 +6065,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129610357</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5939,6 +6179,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680912</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6048,6 +6293,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680938</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6150,6 +6400,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466244</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6261,6 +6516,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609007</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6358,6 +6618,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120208775</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6455,6 +6720,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120208776</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6561,6 +6831,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609173</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6667,6 +6942,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609694</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6769,6 +7049,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609702</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6871,6 +7156,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609896</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6985,6 +7275,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609756</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7087,6 +7382,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609743</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7184,6 +7484,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466278</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7281,6 +7586,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120208682</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7379,6 +7689,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129608936</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7476,6 +7791,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120208739</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7586,6 +7906,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609325</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7683,6 +8008,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124393207</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7780,6 +8110,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124393208</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7882,6 +8217,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129608923</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7984,6 +8324,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609001</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8086,6 +8431,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609073</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8188,6 +8538,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609100</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8290,6 +8645,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609244</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8392,6 +8752,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609548</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8494,6 +8859,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609695</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8596,6 +8966,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609751</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8693,6 +9068,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466301</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8790,6 +9170,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466303</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8914,6 +9299,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609783</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9038,6 +9428,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680905</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9171,6 +9566,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129707800</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9304,8 +9704,95 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>